--- a/new-info55/web.xlsx
+++ b/new-info55/web.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info55\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25080" windowHeight="8295"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>domain</t>
   </si>
@@ -44,28 +49,31 @@
     <t>date</t>
   </si>
   <si>
-    <t>read.cabledfluting.com</t>
+    <t>hub.cabledfluting.com</t>
+  </si>
+  <si>
+    <t>#6090b8</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>read.aqueduct.fun</t>
+  </si>
+  <si>
+    <t>#c4b091</t>
+  </si>
+  <si>
+    <t>sec.aqueduct.fun</t>
   </si>
   <si>
     <t>#664b3a</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>read.aqueduct.fun</t>
-  </si>
-  <si>
-    <t>#c4b091</t>
-  </si>
-  <si>
-    <t>sec.aqueduct.fun</t>
   </si>
   <si>
     <t>play.jitter.site</t>
@@ -190,7 +198,7 @@
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -362,7 +370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +404,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF664B3A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6090B8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -716,7 +730,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,16 +754,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -758,85 +772,85 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -874,14 +888,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1299,15 +1313,15 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="16">
-        <v>46230</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1485,7 +1499,7 @@
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="A2" r:id="rId3" display="read.cabledfluting.com" tooltip="https://read.cabledfluting.com"/>
+    <hyperlink ref="A2" r:id="rId3" display="hub.cabledfluting.com" tooltip="http://cabledfluting.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1532,14 +1546,14 @@
       <c r="E2" s="7">
         <v>3</v>
       </c>
-      <c r="F2" s="13"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>5</v>
+      <c r="B3" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7">
@@ -1548,7 +1562,7 @@
       <c r="E3" s="7">
         <v>3</v>
       </c>
-      <c r="F3" s="13"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="7"/>
@@ -1556,7 +1570,7 @@
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="13"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="7"/>
@@ -1564,7 +1578,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="13"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="7"/>
@@ -1572,7 +1586,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7"/>
@@ -1580,7 +1594,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="13"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7"/>
@@ -1588,7 +1602,7 @@
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="13"/>
+      <c r="F8" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1624,10 +1638,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7">
@@ -1639,10 +1653,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7">
@@ -1745,53 +1759,53 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1" spans="1:8">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" ht="52" customHeight="1" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -1799,11 +1813,11 @@
     <row r="4" ht="74" customHeight="1" spans="1:8">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1812,16 +1826,16 @@
     </row>
     <row r="5" ht="100" customHeight="1" spans="1:8">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
